--- a/dcf/OKTA.xlsx
+++ b/dcf/OKTA.xlsx
@@ -361,87 +361,87 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C21" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 14.0x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -877,7 +877,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1132,184 +1132,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>76.57928794875288</v>
+        <v>84.87980503059244</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>74.18300295563293</v>
+        <v>82.10006591494684</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>71.89923389862764</v>
+        <v>79.45223845115126</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>69.72204658560028</v>
+        <v>76.92932310887043</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>67.64584941536522</v>
+        <v>74.52472605044287</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>65.66537200544145</v>
+        <v>72.23223375182542</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>63.77564524862242</v>
+        <v>70.04598932371488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>80.72954648967266</v>
+        <v>89.03006357151222</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>78.14153443528988</v>
+        <v>86.05859739460379</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>75.67573617488945</v>
+        <v>83.22874072741307</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>73.32568484723535</v>
+        <v>80.5329613705055</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>71.08528773290404</v>
+        <v>77.96416436798168</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>68.94880287863344</v>
+        <v>75.51566462501739</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>66.91081728616865</v>
+        <v>73.18116136126109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>84.87980503059244</v>
+        <v>93.18032211243201</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>82.10006591494684</v>
+        <v>90.01712887426075</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>79.45223845115126</v>
+        <v>87.00524300367486</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>76.92932310887043</v>
+        <v>84.13659963214057</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>74.52472605044287</v>
+        <v>81.40360268552051</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>72.23223375182542</v>
+        <v>78.79909549820935</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>70.04598932371488</v>
+        <v>76.31633339880732</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>89.03006357151222</v>
+        <v>97.33058065335179</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>86.05859739460379</v>
+        <v>93.9756603539177</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>83.22874072741307</v>
+        <v>90.78174527993669</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>80.5329613705055</v>
+        <v>87.74023789377566</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>77.96416436798168</v>
+        <v>84.84304100305933</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>75.51566462501739</v>
+        <v>82.08252637140134</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>73.18116136126109</v>
+        <v>79.45150543635354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>93.18032211243201</v>
+        <v>101.4808391942716</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>90.01712887426075</v>
+        <v>97.93419183357464</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>87.00524300367486</v>
+        <v>94.55824755619849</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>84.13659963214057</v>
+        <v>91.34387615541071</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>81.40360268552051</v>
+        <v>88.28247932059813</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>78.79909549820935</v>
+        <v>85.3659572445933</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>76.31633339880732</v>
+        <v>82.58667747389977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>97.33058065335179</v>
+        <v>105.6310977351913</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>93.9756603539177</v>
+        <v>101.8927233132316</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>90.78174527993669</v>
+        <v>98.3347498324603</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>87.74023789377566</v>
+        <v>94.9475144170458</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>84.84304100305933</v>
+        <v>91.72191763813694</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>82.08252637140134</v>
+        <v>88.64938811778528</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>79.45150543635354</v>
+        <v>85.72184951144598</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>101.4808391942716</v>
+        <v>109.7813562761111</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>97.93419183357464</v>
+        <v>105.8512547928886</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>94.55824755619849</v>
+        <v>102.1112521087221</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>91.34387615541071</v>
+        <v>98.55115267868086</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>88.28247932059813</v>
+        <v>95.16135595567577</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>85.3659572445933</v>
+        <v>91.93281899097725</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>82.58667747389977</v>
+        <v>88.85702154899221</v>
       </c>
     </row>
     <row r="13">
@@ -1332,7 +1332,7 @@
         <v>0.06963999999999999</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.8323176906743555</v>
+        <v>0.8227236544150027</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24395,7 +24395,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>80.5329613705055</v>
+        <v>87.74023789377566</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>108.8251393535351</v>
+        <v>118.2605116071436</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>59.91212314800111</v>
+        <v>65.35372402918051</v>
       </c>
     </row>
     <row r="59">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24824,7 +24824,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24832,7 +24832,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24851,7 +24855,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24859,7 +24863,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24878,7 +24886,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24886,7 +24894,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24905,7 +24917,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24913,7 +24925,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24932,7 +24948,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24940,7 +24956,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24959,7 +24979,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24967,7 +24987,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24986,7 +25010,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24994,7 +25018,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25013,7 +25041,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -25021,7 +25049,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25040,7 +25072,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25048,7 +25080,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25067,7 +25103,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25075,7 +25111,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25094,7 +25134,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25102,7 +25142,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25121,7 +25165,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25129,7 +25173,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25148,7 +25196,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -25156,7 +25204,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr"/>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25175,7 +25227,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25183,7 +25235,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25202,12 +25258,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.0x</t>
         </is>
       </c>
       <c r="F22" s="31" t="inlineStr"/>
@@ -25229,7 +25285,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -25237,7 +25293,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr"/>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25256,7 +25316,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/dcf/OKTA.xlsx
+++ b/dcf/OKTA.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>141.4199981689453</v>
+        <v>151.2700042724609</v>
       </c>
     </row>
     <row r="14">
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>141.4199981689453</v>
+        <v>151.2700042724609</v>
       </c>
     </row>
     <row r="49">
